--- a/data/trans_dic/P43-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P43-Edad-trans_dic.xlsx
@@ -505,7 +505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N20"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -518,22 +518,18 @@
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que le han realizado alguna vez una mamografía por prescripción de algún especialista</t>
+          <t>Población a la que le han realizado alguna vez una mamografía por prescripción de algún especialista (tasa de respuesta: 99,33%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,20 +537,12 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="L1" s="3" t="n"/>
-      <c r="M1" s="3" t="n"/>
-      <c r="N1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -595,26 +583,6 @@
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2007</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="M2" s="3" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="N2" s="3" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
@@ -631,10 +599,6 @@
       <c r="H3" s="2" t="n"/>
       <c r="I3" s="2" t="n"/>
       <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
-      <c r="L3" s="2" t="n"/>
-      <c r="M3" s="2" t="n"/>
-      <c r="N3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -649,22 +613,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,26 +647,6 @@
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>8,07%</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>5,74%</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>6,39%</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>5,56%</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>8,07%</t>
         </is>
@@ -717,62 +661,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>3,95; 8,17</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>4,18; 9,22</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>3,57; 8,27</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>4,02; 14,08</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,09; 8,13</t>
+          <t>3,95; 8,17</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,95; 8,81</t>
+          <t>4,18; 9,22</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,56; 8,3</t>
+          <t>3,57; 8,27</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,4; 13,44</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>4,09; 8,13</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>3,95; 8,81</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>3,56; 8,3</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>4,4; 13,44</t>
+          <t>4,02; 14,08</t>
         </is>
       </c>
     </row>
@@ -789,22 +713,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,26 +747,6 @@
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>13,13%</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>13,05%</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>13,2%</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>13,41%</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>13,13%</t>
         </is>
@@ -857,62 +761,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>10,36; 15,87</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>10,38; 16,01</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>10,8; 16,35</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>6,83; 17,84</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,33; 16,1</t>
+          <t>10,36; 15,87</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,42; 15,93</t>
+          <t>10,38; 16,01</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,89; 16,46</t>
+          <t>10,8; 16,35</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,22; 17,92</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>10,33; 16,1</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>10,42; 15,93</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>10,89; 16,46</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>7,22; 17,92</t>
+          <t>6,83; 17,84</t>
         </is>
       </c>
     </row>
@@ -929,22 +813,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>34,36%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>33,98%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,26 +847,6 @@
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>33,98%</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>33,95%</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>33,3%</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>34,36%</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>33,98%</t>
         </is>
@@ -997,62 +861,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>30,24; 37,57</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>29,68; 36,97</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>30,62; 38,2</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>30,1; 37,86</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>30,51; 37,77</t>
+          <t>30,24; 37,57</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>29,93; 37,26</t>
+          <t>29,68; 36,97</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>30,96; 38,3</t>
+          <t>30,62; 38,2</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>29,54; 37,99</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>30,51; 37,77</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>29,93; 37,26</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>30,96; 38,3</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>29,54; 37,99</t>
+          <t>30,1; 37,86</t>
         </is>
       </c>
     </row>
@@ -1069,22 +913,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>61,89%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>66,73%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>66,05%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>64,63%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,26 +947,6 @@
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>64,63%</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>61,89%</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>66,73%</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>66,05%</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>64,63%</t>
         </is>
@@ -1137,62 +961,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>57,39; 66,12</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>62,49; 70,5</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>62,1; 69,3</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>59,97; 71,76</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>57,87; 66,16</t>
+          <t>57,39; 66,12</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>62,78; 70,81</t>
+          <t>62,49; 70,5</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>62,36; 69,78</t>
+          <t>62,1; 69,3</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>60,34; 71,65</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>57,87; 66,16</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>62,78; 70,81</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>62,36; 69,78</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>60,34; 71,65</t>
+          <t>59,97; 71,76</t>
         </is>
       </c>
     </row>
@@ -1209,22 +1013,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>75,64%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>91,54%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>80,33%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,26 +1047,6 @@
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>80,33%</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>75,64%</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>91,54%</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>90,34%</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>80,33%</t>
         </is>
@@ -1277,62 +1061,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>71,25; 79,86</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>88,34; 94,19</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>86,97; 93,2</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>77,14; 83,04</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>71,08; 79,67</t>
+          <t>71,25; 79,86</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>88,42; 93,92</t>
+          <t>88,34; 94,19</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>87,03; 92,69</t>
+          <t>86,97; 93,2</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>77,43; 83,32</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>71,08; 79,67</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>88,42; 93,92</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>87,03; 92,69</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>77,43; 83,32</t>
+          <t>77,14; 83,04</t>
         </is>
       </c>
     </row>
@@ -1349,22 +1113,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>63,43%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>85,31%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>86,01%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>90,47%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1383,26 +1147,6 @@
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>90,47%</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>63,43%</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>85,31%</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>86,01%</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>90,47%</t>
         </is>
@@ -1417,62 +1161,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>58,57; 67,93</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>81,19; 89,21</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>81,74; 89,54</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>83,73; 96,94</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>58,19; 68,53</t>
+          <t>58,57; 67,93</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>81,28; 88,86</t>
+          <t>81,19; 89,21</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>82,5; 89,29</t>
+          <t>81,74; 89,54</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>83,51; 96,85</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>58,19; 68,53</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>81,28; 88,86</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>82,5; 89,29</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>83,51; 96,85</t>
+          <t>83,73; 96,94</t>
         </is>
       </c>
     </row>
@@ -1489,22 +1213,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>53,8%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>59,98%</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>70,39%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1523,26 +1247,6 @@
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>70,39%</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>29,05%</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>53,8%</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>59,98%</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>70,39%</t>
         </is>
@@ -1557,62 +1261,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>24,05; 34,53</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>48,62; 59,16</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>54,22; 65,11</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>66,95; 73,61</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>24,23; 34,45</t>
+          <t>24,05; 34,53</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>48,43; 59,39</t>
+          <t>48,62; 59,16</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>53,79; 65,45</t>
+          <t>54,22; 65,11</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>66,98; 73,71</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>24,23; 34,45</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>48,43; 59,39</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>53,79; 65,45</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>66,98; 73,71</t>
+          <t>66,95; 73,61</t>
         </is>
       </c>
     </row>
@@ -1629,22 +1313,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>37,91%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>47,14%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>49,93%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>55,92%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1663,26 +1347,6 @@
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>55,92%</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>37,91%</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>47,14%</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>49,93%</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>55,92%</t>
         </is>
@@ -1697,62 +1361,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>36,25; 39,49</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>45,45; 48,86</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>48,25; 51,83</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>51,07; 66,18</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>36,19; 39,57</t>
+          <t>36,25; 39,49</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>45,44; 48,92</t>
+          <t>45,45; 48,86</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>48,16; 51,62</t>
+          <t>48,25; 51,83</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>51,38; 66,52</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>36,19; 39,57</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>45,44; 48,92</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>48,16; 51,62</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>51,38; 66,52</t>
+          <t>51,07; 66,18</t>
         </is>
       </c>
     </row>
@@ -1764,17 +1408,16 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="11">
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A10:A11"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="A16:A17"/>
     <mergeCell ref="G1:J1"/>
     <mergeCell ref="A6:A7"/>
-    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A10:A11"/>
     <mergeCell ref="A18:A19"/>
     <mergeCell ref="A14:A15"/>
   </mergeCells>
@@ -1788,7 +1431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N28"/>
+  <dimension ref="A1:J28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1801,22 +1444,18 @@
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que le han realizado alguna vez una mamografía por prescripción de algún especialista</t>
+          <t>Población a la que le han realizado alguna vez una mamografía por prescripción de algún especialista (tasa de respuesta: 99,33%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1824,20 +1463,12 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="L1" s="3" t="n"/>
-      <c r="M1" s="3" t="n"/>
-      <c r="N1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -1878,26 +1509,6 @@
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2007</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="M2" s="3" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="N2" s="3" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
@@ -1914,10 +1525,6 @@
       <c r="H3" s="2" t="n"/>
       <c r="I3" s="2" t="n"/>
       <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
-      <c r="L3" s="2" t="n"/>
-      <c r="M3" s="2" t="n"/>
-      <c r="N3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -1932,22 +1539,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>28</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>25</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1966,26 +1573,6 @@
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -2000,22 +1587,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>26696</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>27387</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>21550</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>21297</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2034,26 +1621,6 @@
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>21297</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>26696</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>27387</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>21550</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>21297</t>
         </is>
@@ -2068,62 +1635,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>18380; 37967</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>17921; 39485</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>13836; 32066</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>10610; 37155</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>19026; 37775</t>
+          <t>18380; 37967</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16926; 37739</t>
+          <t>17921; 39485</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13782; 32195</t>
+          <t>13836; 32066</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>11611; 35449</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>19026; 37775</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>16926; 37739</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>13782; 32195</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>11611; 35449</t>
+          <t>10610; 37155</t>
         </is>
       </c>
     </row>
@@ -2140,22 +1687,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>75</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>74</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>78</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>52</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2174,26 +1721,6 @@
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>52</t>
         </is>
@@ -2208,22 +1735,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>81512</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>79982</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>75300</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>51913</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2242,26 +1769,6 @@
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>51913</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>81512</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>79982</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>75300</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>51913</t>
         </is>
@@ -2276,62 +1783,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>64680; 99125</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>62853; 96967</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>60676; 91820</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>26992; 70509</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>64505; 100576</t>
+          <t>64680; 99125</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>63119; 96521</t>
+          <t>62853; 96967</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>61142; 92410</t>
+          <t>60676; 91820</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>28550; 70824</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>64505; 100576</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>63119; 96521</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>61142; 92410</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>28550; 70824</t>
+          <t>26992; 70509</t>
         </is>
       </c>
     </row>
@@ -2348,22 +1835,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>223</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>217</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>228</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>200</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -2382,26 +1869,6 @@
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>217</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>228</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>200</t>
         </is>
@@ -2416,22 +1883,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>233845</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>235383</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>226055</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>126206</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2450,26 +1917,6 @@
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>126206</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>233845</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>235383</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>226055</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>126206</t>
         </is>
@@ -2484,62 +1931,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>208264; 258799</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>209763; 261305</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>201454; 251365</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>111763; 140611</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>210111; 260155</t>
+          <t>208264; 258799</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>211586; 263375</t>
+          <t>209763; 261305</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>203709; 251979</t>
+          <t>201454; 251365</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>109701; 141079</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>210111; 260155</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>211586; 263375</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>203709; 251979</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>109701; 141079</t>
+          <t>111763; 140611</t>
         </is>
       </c>
     </row>
@@ -2556,22 +1983,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>312</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>358</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>397</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>501</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -2590,26 +2017,6 @@
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>501</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>312</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>358</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>397</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>501</t>
         </is>
@@ -2624,22 +2031,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>317458</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>410514</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>427426</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>326992</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2658,26 +2065,6 @@
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>326992</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>317458</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>410514</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>427426</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>326992</t>
         </is>
@@ -2692,62 +2079,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>294349; 339156</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>384436; 433670</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>401839; 448460</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>303418; 363052</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>296836; 339375</t>
+          <t>294349; 339156</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>386184; 435566</t>
+          <t>384436; 433670</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>403526; 451511</t>
+          <t>401839; 448460</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>305300; 362520</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>296836; 339375</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>386184; 435566</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>403526; 451511</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>305300; 362520</t>
+          <t>303418; 363052</t>
         </is>
       </c>
     </row>
@@ -2764,22 +2131,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>297</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>370</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>390</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>599</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2798,26 +2165,6 @@
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>599</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>297</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>370</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>390</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>599</t>
         </is>
@@ -2832,22 +2179,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>303417</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>408088</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>446851</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>322252</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2866,26 +2213,6 @@
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>322252</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>303417</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>408088</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>446851</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>322252</t>
         </is>
@@ -2900,62 +2227,42 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>285802; 320313</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>393822; 419907</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>430164; 460956</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>309451; 333123</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>285126; 319562</t>
+          <t>285802; 320313</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>394208; 418736</t>
+          <t>393822; 419907</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>430455; 458454</t>
+          <t>430164; 460956</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>310612; 334256</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>285126; 319562</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>394208; 418736</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>430455; 458454</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>310612; 334256</t>
+          <t>309451; 333123</t>
         </is>
       </c>
     </row>
@@ -2972,22 +2279,22 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>233</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>294</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>302</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>561</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -3006,26 +2313,6 @@
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>561</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>233</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>294</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>302</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>561</t>
         </is>
@@ -3040,22 +2327,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>215164</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>299497</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>323145</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>476092</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3074,26 +2361,6 @@
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>476092</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>215164</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>299497</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>323145</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>476092</t>
         </is>
@@ -3108,62 +2375,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>198672; 230404</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>285028; 313192</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>307069; 336383</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>440606; 510159</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>197362; 232455</t>
+          <t>198672; 230404</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>285355; 311949</t>
+          <t>285028; 313192</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>309945; 335445</t>
+          <t>307069; 336383</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>439496; 509652</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>197362; 232455</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>285355; 311949</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>309945; 335445</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>439496; 509652</t>
+          <t>440606; 510159</t>
         </is>
       </c>
     </row>
@@ -3180,22 +2427,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>84</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>185</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>178</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>542</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -3214,26 +2461,6 @@
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>542</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>185</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>542</t>
         </is>
@@ -3248,22 +2475,22 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>95351</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>206399</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>236972</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>258386</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3282,26 +2509,6 @@
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>258386</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>95351</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>206399</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>236972</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>258386</t>
         </is>
@@ -3316,62 +2523,42 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>78953; 113346</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>186522; 226943</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>214220; 257258</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>245766; 270191</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>79520; 113078</t>
+          <t>78953; 113346</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>185780; 227810</t>
+          <t>186522; 226943</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>212549; 258599</t>
+          <t>214220; 257258</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>245839; 270560</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>79520; 113078</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>185780; 227810</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>212549; 258599</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>245839; 270560</t>
+          <t>245766; 270191</t>
         </is>
       </c>
     </row>
@@ -3388,22 +2575,22 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1252</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1523</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1595</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2467</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3422,26 +2609,6 @@
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>2467</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>1252</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>1523</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>1595</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>2467</t>
         </is>
@@ -3456,22 +2623,22 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1273441</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1667249</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1757300</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1583137</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3490,26 +2657,6 @@
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>1583137</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>1273441</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>1667249</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>1757300</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>1583137</t>
         </is>
@@ -3524,62 +2671,42 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1217806; 1326804</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1607282; 1727835</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1698387; 1824187</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1445705; 1873457</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1215683; 1329323</t>
+          <t>1217806; 1326804</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1606844; 1729955</t>
+          <t>1607282; 1727835</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1694936; 1816789</t>
+          <t>1698387; 1824187</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>1454515; 1883137</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>1215683; 1329323</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>1606844; 1729955</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>1694936; 1816789</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t>1454515; 1883137</t>
+          <t>1445705; 1873457</t>
         </is>
       </c>
     </row>
@@ -3591,17 +2718,16 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="11">
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A16:A18"/>
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="A25:A27"/>
     <mergeCell ref="A19:A21"/>
-    <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A1:B2"/>
     <mergeCell ref="A22:A24"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>

--- a/data/trans_dic/P43-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P43-Edad-trans_dic.xlsx
@@ -628,7 +628,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>7,26%</t>
         </is>
       </c>
     </row>
@@ -661,42 +661,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,95; 8,17</t>
+          <t>3,92; 8,14</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,18; 9,22</t>
+          <t>3,96; 9,17</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,57; 8,27</t>
+          <t>3,67; 7,9</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,02; 14,08</t>
+          <t>4,14; 12,51</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,95; 8,17</t>
+          <t>3,92; 8,14</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,18; 9,22</t>
+          <t>3,96; 9,17</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,57; 8,27</t>
+          <t>3,67; 7,9</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,02; 14,08</t>
+          <t>4,14; 12,51</t>
         </is>
       </c>
     </row>
@@ -728,7 +728,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -748,7 +748,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>14,51%</t>
         </is>
       </c>
     </row>
@@ -761,42 +761,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>10,36; 15,87</t>
+          <t>10,63; 16,34</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10,38; 16,01</t>
+          <t>10,85; 16,34</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10,8; 16,35</t>
+          <t>10,79; 16,2</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,83; 17,84</t>
+          <t>11,03; 18,68</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,36; 15,87</t>
+          <t>10,63; 16,34</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,38; 16,01</t>
+          <t>10,85; 16,34</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,8; 16,35</t>
+          <t>10,79; 16,2</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,83; 17,84</t>
+          <t>11,03; 18,68</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>33,38%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -848,7 +848,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>33,38%</t>
         </is>
       </c>
     </row>
@@ -861,42 +861,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>30,24; 37,57</t>
+          <t>30,45; 37,59</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>29,68; 36,97</t>
+          <t>29,73; 36,99</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>30,62; 38,2</t>
+          <t>30,63; 38,09</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>30,1; 37,86</t>
+          <t>29,44; 37,12</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>30,24; 37,57</t>
+          <t>30,45; 37,59</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>29,68; 36,97</t>
+          <t>29,73; 36,99</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>30,62; 38,2</t>
+          <t>30,63; 38,09</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>30,1; 37,86</t>
+          <t>29,44; 37,12</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>64,63%</t>
+          <t>61,78%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -948,7 +948,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>64,63%</t>
+          <t>61,78%</t>
         </is>
       </c>
     </row>
@@ -961,42 +961,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>57,39; 66,12</t>
+          <t>57,19; 66,15</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>62,49; 70,5</t>
+          <t>62,69; 70,71</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>62,1; 69,3</t>
+          <t>62,16; 69,57</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>59,97; 71,76</t>
+          <t>58,1; 65,14</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>57,39; 66,12</t>
+          <t>57,19; 66,15</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>62,49; 70,5</t>
+          <t>62,69; 70,71</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>62,1; 69,3</t>
+          <t>62,16; 69,57</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>59,97; 71,76</t>
+          <t>58,1; 65,14</t>
         </is>
       </c>
     </row>
@@ -1028,7 +1028,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>80,33%</t>
+          <t>79,63%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>80,33%</t>
+          <t>79,63%</t>
         </is>
       </c>
     </row>
@@ -1061,42 +1061,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>71,25; 79,86</t>
+          <t>71,61; 79,8</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>88,34; 94,19</t>
+          <t>88,52; 94,03</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>86,97; 93,2</t>
+          <t>87,21; 92,83</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>77,14; 83,04</t>
+          <t>76,49; 82,41</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>71,25; 79,86</t>
+          <t>71,61; 79,8</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>88,34; 94,19</t>
+          <t>88,52; 94,03</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>86,97; 93,2</t>
+          <t>87,21; 92,83</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>77,14; 83,04</t>
+          <t>76,49; 82,41</t>
         </is>
       </c>
     </row>
@@ -1128,7 +1128,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>85,09%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>85,09%</t>
         </is>
       </c>
     </row>
@@ -1161,42 +1161,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>58,57; 67,93</t>
+          <t>58,57; 68,49</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>81,19; 89,21</t>
+          <t>80,61; 88,84</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>81,74; 89,54</t>
+          <t>82,12; 89,29</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>83,73; 96,94</t>
+          <t>82,02; 87,72</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>58,57; 67,93</t>
+          <t>58,57; 68,49</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>81,19; 89,21</t>
+          <t>80,61; 88,84</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>81,74; 89,54</t>
+          <t>82,12; 89,29</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>83,73; 96,94</t>
+          <t>82,02; 87,72</t>
         </is>
       </c>
     </row>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>70,39%</t>
+          <t>70,22%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>70,39%</t>
+          <t>70,22%</t>
         </is>
       </c>
     </row>
@@ -1261,42 +1261,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>24,05; 34,53</t>
+          <t>23,91; 34,57</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>48,62; 59,16</t>
+          <t>48,38; 59,01</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>54,22; 65,11</t>
+          <t>54,29; 65,7</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>66,95; 73,61</t>
+          <t>66,6; 73,53</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>24,05; 34,53</t>
+          <t>23,91; 34,57</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>48,62; 59,16</t>
+          <t>48,38; 59,01</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>54,22; 65,11</t>
+          <t>54,29; 65,7</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>66,95; 73,61</t>
+          <t>66,6; 73,53</t>
         </is>
       </c>
     </row>
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>55,92%</t>
+          <t>52,32%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>55,92%</t>
+          <t>52,32%</t>
         </is>
       </c>
     </row>
@@ -1361,42 +1361,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>36,25; 39,49</t>
+          <t>36,16; 39,59</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>45,45; 48,86</t>
+          <t>45,56; 48,86</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>48,25; 51,83</t>
+          <t>48,24; 51,71</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>51,07; 66,18</t>
+          <t>50,59; 53,89</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>36,25; 39,49</t>
+          <t>36,16; 39,59</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>45,45; 48,86</t>
+          <t>45,56; 48,86</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>48,25; 51,83</t>
+          <t>48,24; 51,71</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>51,07; 66,18</t>
+          <t>50,59; 53,89</t>
         </is>
       </c>
     </row>
@@ -1602,7 +1602,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21297</t>
+          <t>21938</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1622,7 +1622,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>21297</t>
+          <t>21938</t>
         </is>
       </c>
     </row>
@@ -1635,42 +1635,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>18380; 37967</t>
+          <t>18205; 37832</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>17921; 39485</t>
+          <t>16977; 39274</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13836; 32066</t>
+          <t>14243; 30632</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10610; 37155</t>
+          <t>12527; 37831</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>18380; 37967</t>
+          <t>18205; 37832</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17921; 39485</t>
+          <t>16977; 39274</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13836; 32066</t>
+          <t>14243; 30632</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>10610; 37155</t>
+          <t>12527; 37831</t>
         </is>
       </c>
     </row>
@@ -1750,7 +1750,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>51913</t>
+          <t>53580</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>51913</t>
+          <t>53580</t>
         </is>
       </c>
     </row>
@@ -1783,42 +1783,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>64680; 99125</t>
+          <t>66409; 102058</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>62853; 96967</t>
+          <t>65738; 99004</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>60676; 91820</t>
+          <t>60571; 90990</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>26992; 70509</t>
+          <t>40715; 68964</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>64680; 99125</t>
+          <t>66409; 102058</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>62853; 96967</t>
+          <t>65738; 99004</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>60676; 91820</t>
+          <t>60571; 90990</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>26992; 70509</t>
+          <t>40715; 68964</t>
         </is>
       </c>
     </row>
@@ -1898,7 +1898,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>126206</t>
+          <t>141599</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>126206</t>
+          <t>141599</t>
         </is>
       </c>
     </row>
@@ -1931,42 +1931,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>208264; 258799</t>
+          <t>209760; 258919</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>209763; 261305</t>
+          <t>210141; 261429</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>201454; 251365</t>
+          <t>201511; 250641</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>111763; 140611</t>
+          <t>124901; 157486</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>208264; 258799</t>
+          <t>209760; 258919</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>209763; 261305</t>
+          <t>210141; 261429</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>201454; 251365</t>
+          <t>201511; 250641</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>111763; 140611</t>
+          <t>124901; 157486</t>
         </is>
       </c>
     </row>
@@ -2046,7 +2046,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>326992</t>
+          <t>316513</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>326992</t>
+          <t>316513</t>
         </is>
       </c>
     </row>
@@ -2079,42 +2079,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>294349; 339156</t>
+          <t>293328; 339302</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>384436; 433670</t>
+          <t>385637; 434968</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>401839; 448460</t>
+          <t>402216; 450180</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>303418; 363052</t>
+          <t>297700; 333761</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>294349; 339156</t>
+          <t>293328; 339302</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>384436; 433670</t>
+          <t>385637; 434968</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>401839; 448460</t>
+          <t>402216; 450180</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>303418; 363052</t>
+          <t>297700; 333761</t>
         </is>
       </c>
     </row>
@@ -2194,7 +2194,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>322252</t>
+          <t>355760</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2214,7 +2214,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>322252</t>
+          <t>355760</t>
         </is>
       </c>
     </row>
@@ -2227,42 +2227,42 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>285802; 320313</t>
+          <t>287235; 320077</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>393822; 419907</t>
+          <t>394657; 419215</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>430164; 460956</t>
+          <t>431337; 459151</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>309451; 333123</t>
+          <t>341704; 368182</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>285802; 320313</t>
+          <t>287235; 320077</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>393822; 419907</t>
+          <t>394657; 419215</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>430164; 460956</t>
+          <t>431337; 459151</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>309451; 333123</t>
+          <t>341704; 368182</t>
         </is>
       </c>
     </row>
@@ -2342,7 +2342,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>476092</t>
+          <t>296622</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>476092</t>
+          <t>296622</t>
         </is>
       </c>
     </row>
@@ -2375,42 +2375,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>198672; 230404</t>
+          <t>198652; 232308</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>285028; 313192</t>
+          <t>282980; 311888</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>307069; 336383</t>
+          <t>308531; 335436</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>440606; 510159</t>
+          <t>285904; 305785</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>198672; 230404</t>
+          <t>198652; 232308</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>285028; 313192</t>
+          <t>282980; 311888</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>307069; 336383</t>
+          <t>308531; 335436</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>440606; 510159</t>
+          <t>285904; 305785</t>
         </is>
       </c>
     </row>
@@ -2490,7 +2490,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>258386</t>
+          <t>280479</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>258386</t>
+          <t>280479</t>
         </is>
       </c>
     </row>
@@ -2523,42 +2523,42 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>78953; 113346</t>
+          <t>78472; 113475</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>186522; 226943</t>
+          <t>185596; 226352</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>214220; 257258</t>
+          <t>214513; 259608</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>245766; 270191</t>
+          <t>266020; 293725</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>78953; 113346</t>
+          <t>78472; 113475</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>186522; 226943</t>
+          <t>185596; 226352</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>214220; 257258</t>
+          <t>214513; 259608</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>245766; 270191</t>
+          <t>266020; 293725</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1583137</t>
+          <t>1466492</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -2658,7 +2658,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>1583137</t>
+          <t>1466492</t>
         </is>
       </c>
     </row>
@@ -2671,42 +2671,42 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1217806; 1326804</t>
+          <t>1214792; 1330182</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1607282; 1727835</t>
+          <t>1611161; 1727789</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1698387; 1824187</t>
+          <t>1697844; 1820096</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1445705; 1873457</t>
+          <t>1418108; 1510341</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1217806; 1326804</t>
+          <t>1214792; 1330182</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1607282; 1727835</t>
+          <t>1611161; 1727789</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1698387; 1824187</t>
+          <t>1697844; 1820096</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>1445705; 1873457</t>
+          <t>1418108; 1510341</t>
         </is>
       </c>
     </row>
